--- a/result/result_sample_input.xlsx
+++ b/result/result_sample_input.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>供应商</t>
   </si>
@@ -28,7 +28,13 @@
     <t>任务令</t>
   </si>
   <si>
-    <t>满足量</t>
+    <t>线体</t>
+  </si>
+  <si>
+    <t>货位</t>
+  </si>
+  <si>
+    <t>任务令满足量</t>
   </si>
   <si>
     <t>包规</t>
@@ -37,27 +43,21 @@
     <t>装载板数</t>
   </si>
   <si>
+    <t>装载量</t>
+  </si>
+  <si>
     <t>总装载板数</t>
   </si>
   <si>
     <t>车规</t>
   </si>
   <si>
+    <t>装载率</t>
+  </si>
+  <si>
     <t>到达时间</t>
   </si>
   <si>
-    <t>装载率</t>
-  </si>
-  <si>
-    <t>s_group</t>
-  </si>
-  <si>
-    <t>sv_group</t>
-  </si>
-  <si>
-    <t>svi_group</t>
-  </si>
-  <si>
     <t>supplier1</t>
   </si>
   <si>
@@ -73,13 +73,19 @@
     <t>mfg_order1</t>
   </si>
   <si>
+    <t>line1</t>
+  </si>
+  <si>
+    <t>loc1</t>
+  </si>
+  <si>
+    <t>11.11%</t>
+  </si>
+  <si>
+    <t>9.09%</t>
+  </si>
+  <si>
     <t>2026-06-09 21:00:00</t>
-  </si>
-  <si>
-    <t>11.11%</t>
-  </si>
-  <si>
-    <t>9.09%</t>
   </si>
 </sst>
 </file>
@@ -471,35 +477,35 @@
       <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2">
         <v>60</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>30</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="J2">
+        <v>60</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
-      <c r="I2">
+      <c r="L2">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -515,35 +521,35 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3">
         <v>40</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>30</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="J3">
+        <v>60</v>
+      </c>
+      <c r="K3">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/result/result_sample_input.xlsx
+++ b/result/result_sample_input.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>供应商</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>9.09%</t>
+  </si>
+  <si>
+    <t>2026-06-09 20:00:00</t>
   </si>
   <si>
     <t>2026-06-09 21:00:00</t>
@@ -484,7 +487,7 @@
         <v>20</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -528,7 +531,7 @@
         <v>20</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
         <v>30</v>
@@ -549,7 +552,7 @@
         <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/result/result_sample_input.xlsx
+++ b/result/result_sample_input.xlsx
@@ -487,7 +487,7 @@
         <v>20</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -531,7 +531,7 @@
         <v>20</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>30</v>
